--- a/outputs/evaluation/architecture/validation/CF_M06/run_2/CF_M06_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_2/CF_M06_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Third-party companies that offer digital signage service/consulting using Waapiti technology.</t>
+          <t>Third-party companies that offer digital signage service/consultancy using Waapiti technology.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -540,22 +540,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The mobile application uses AWS SNS for push notifications.</t>
+          <t>The application uses AWS SNS for the delivery of push notifications.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>91,92</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_01, AU_16</t>
+          <t>AU_03, AU_09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>mobile device, aws sns</t>
+          <t>waapiti platform, aws sns</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -575,7 +575,103 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.86</v>
+        <v>0.8771</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>The application uses sockets to receive logs in real time from the server.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>38,79</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU_04, AU_03</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>presentation layer, waapiti platform</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CF_M06_AU30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>This functionality connects via socket [25] with the server and displays</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7722</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3-Layer Architecture</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>The architecture follows the 3-layer model: Presentation, Domain, and Data.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CF_M06_P01</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Three Layers</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>This architecture follows the 3-layer model</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8511</v>
       </c>
     </row>
   </sheetData>
